--- a/小野町_引継ぎ_整理済/18_年報・国保連データ/小野町_年報・国保連データ整理_20260908.xlsx
+++ b/小野町_引継ぎ_整理済/18_年報・国保連データ/小野町_年報・国保連データ整理_20260908.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>**解決**（年報 様式4）。令和5・6年度末とも12,000,000円</t>
+          <t>**解決**（町の財務書類 附属明細書。令和5年度末120,000千円）。年報 様式4の保有額（令和5・6年度末12,000,000円）は財務書類と合わない</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2045,14 +2045,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>※ **介護給付費準備基金の保有額が、令和4年度末120,000,000円から令和5年度末12,000,000円へ1桁減っている。**取崩の実績か入力桁の誤りかを町に確認する必要がある。第9期が見込んだ基金取崩35,000千円は、令和5年度末の12,000千円を前提とすると実行できない</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>※ 令和3年度の基金保有額が0であるのは未入力の可能性がある</t>
+          <t>※ **年報 様式4の介護給付費準備基金保有額（令和3年度末0円、令和4年度末120,000,000円、令和5・6年度末12,000,000円）は、町の財務書類と合わない。**財務書類では令和4年度末90,000千円・令和5年度末120,000千円で、令和8年度末の見込みは210,000千円。第9期が見込んだ基金取崩35,000千円は、残高の範囲内で実行できる</t>
         </is>
       </c>
     </row>
